--- a/artfynd/A 58718-2021 artfynd.xlsx
+++ b/artfynd/A 58718-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117741262</v>
+        <v>117741247</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>95131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455508</v>
+        <v>455543</v>
       </c>
       <c r="R2" t="n">
-        <v>6653742</v>
+        <v>6653723</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,32 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre granskog med måttligt med död ved. Senvuxet, ca 160 år.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Klen granlåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga med barken kvar.</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117741560</v>
+        <v>117741509</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,49 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV Bråttjärn, Vrm</t>
+          <t>V Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455666</v>
+        <v>455543</v>
       </c>
       <c r="R3" t="n">
-        <v>6653673</v>
+        <v>6653723</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -917,27 +885,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blockig, gammal granskog med inslag av gammal tall.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>På senvuxna, gamla granar. Rikligt spritt.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # På senvuxna, gamla granar. Rikligt spritt.</t>
+          <t>Blockig, gammal granskog med inslag av äldre tall.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117741247</v>
+        <v>117741574</v>
       </c>
       <c r="B4" t="n">
-        <v>95131</v>
+        <v>91772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,41 +919,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Bråttjärn, Vrm</t>
+          <t>NV Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455543</v>
+        <v>455517</v>
       </c>
       <c r="R4" t="n">
-        <v>6653723</v>
+        <v>6653562</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,7 +996,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Talludde i kantzon mot myr i barrdominerad skog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117741509</v>
+        <v>117741560</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
+        <v>78480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,41 +1031,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Bråttjärn, Vrm</t>
+          <t>NV Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455543</v>
+        <v>455666</v>
       </c>
       <c r="R5" t="n">
-        <v>6653723</v>
+        <v>6653673</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1165,7 +1125,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Blockig, gammal granskog med inslag av äldre tall.</t>
+          <t>Blockig, gammal granskog med inslag av gammal tall.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>På senvuxna, gamla granar. Rikligt spritt.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # På senvuxna, gamla granar. Rikligt spritt.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1319,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117741574</v>
+        <v>117741262</v>
       </c>
       <c r="B7" t="n">
-        <v>91772</v>
+        <v>90499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,25 +1311,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1358,14 +1338,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NV Bråttjärn, Vrm</t>
+          <t>V Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455517</v>
+        <v>455508</v>
       </c>
       <c r="R7" t="n">
-        <v>6653562</v>
+        <v>6653742</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1417,7 +1397,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Talludde i kantzon mot myr i barrdominerad skog.</t>
+          <t>Äldre granskog med måttligt med död ved. Senvuxet, ca 160 år.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Klen granlåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 58718-2021 artfynd.xlsx
+++ b/artfynd/A 58718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117741247</v>
       </c>
       <c r="B2" t="n">
-        <v>95131</v>
+        <v>95133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117741509</v>
+        <v>117741303</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455543</v>
+        <v>455508</v>
       </c>
       <c r="R3" t="n">
-        <v>6653723</v>
+        <v>6653742</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,27 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blockig, gammal granskog med inslag av äldre tall.</t>
+          <t>Äldre granskog, på senvuxna granar flera tussar.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Senvuxna granar.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Senvuxna granar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -903,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117741574</v>
+        <v>117741560</v>
       </c>
       <c r="B4" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +935,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455517</v>
+        <v>455666</v>
       </c>
       <c r="R4" t="n">
-        <v>6653562</v>
+        <v>6653673</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1029,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Talludde i kantzon mot myr i barrdominerad skog.</t>
+          <t>Blockig, gammal granskog med inslag av gammal tall.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>På senvuxna, gamla granar. Rikligt spritt.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # På senvuxna, gamla granar. Rikligt spritt.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117741560</v>
+        <v>117741509</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>78571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,49 +1079,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NV Bråttjärn, Vrm</t>
+          <t>V Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455666</v>
+        <v>455543</v>
       </c>
       <c r="R5" t="n">
-        <v>6653673</v>
+        <v>6653723</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,27 +1165,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Blockig, gammal granskog med inslag av gammal tall.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>På senvuxna, gamla granar. Rikligt spritt.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # På senvuxna, gamla granar. Rikligt spritt.</t>
+          <t>Blockig, gammal granskog med inslag av äldre tall.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117741303</v>
+        <v>117741262</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1261,7 +1281,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre granskog, på senvuxna granar flera tussar.</t>
+          <t>Äldre granskog med måttligt med död ved. Senvuxet, ca 160 år.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1276,12 +1296,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Senvuxna granar.</t>
+          <t>Klen granlåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Senvuxna granar.</t>
+          <t>Picea abies # Klen granlåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1299,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117741262</v>
+        <v>117741574</v>
       </c>
       <c r="B7" t="n">
-        <v>90499</v>
+        <v>91774</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,25 +1331,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1338,14 +1358,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V Bråttjärn, Vrm</t>
+          <t>NV Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455508</v>
+        <v>455517</v>
       </c>
       <c r="R7" t="n">
-        <v>6653742</v>
+        <v>6653562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,27 +1417,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre granskog med måttligt med död ved. Senvuxet, ca 160 år.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Klen granlåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga med barken kvar.</t>
+          <t>Talludde i kantzon mot myr i barrdominerad skog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 58718-2021 artfynd.xlsx
+++ b/artfynd/A 58718-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,6 +1571,551 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126380337</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Villastaden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>455520</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6653752</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126380334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Villastaden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>455599</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6653726</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126380336</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96478</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Villastaden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>455505</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6653812</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126380335</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96605</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Villastaden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>455512</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6653807</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126380338</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Villastaden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>455533</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6653753</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58718-2021 artfynd.xlsx
+++ b/artfynd/A 58718-2021 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>126380337</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126380334</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>126380336</v>
       </c>
       <c r="B11" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>126380335</v>
       </c>
       <c r="B12" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>126380338</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 58718-2021 artfynd.xlsx
+++ b/artfynd/A 58718-2021 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117741509</v>
+        <v>126380335</v>
       </c>
       <c r="B2" t="n">
-        <v>78573</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Bråttjärn, Vrm</t>
+          <t>Villastaden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455543</v>
+        <v>455512</v>
       </c>
       <c r="R2" t="n">
-        <v>6653723</v>
+        <v>6653807</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,44 +754,43 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blockig, gammal granskog med inslag av äldre tall.</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117741303</v>
+        <v>117741262</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,7 +880,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre granskog, på senvuxna granar flera tussar.</t>
+          <t>Äldre granskog med måttligt med död ved. Senvuxet, ca 160 år.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -904,12 +895,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Senvuxna granar.</t>
+          <t>Klen granlåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Senvuxna granar.</t>
+          <t>Picea abies # Klen granlåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117741262</v>
+        <v>126380338</v>
       </c>
       <c r="B4" t="n">
-        <v>90503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,19 +947,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Bråttjärn, Vrm</t>
+          <t>Villastaden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455508</v>
+        <v>455533</v>
       </c>
       <c r="R4" t="n">
-        <v>6653742</v>
+        <v>6653753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,12 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,20 +997,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre granskog med måttligt med död ved. Senvuxet, ca 160 år.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1038,25 +1010,20 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Klen granlåga med barken kvar.</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga med barken kvar.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1066,12 +1033,7 @@
         <v>117741247</v>
       </c>
       <c r="B5" t="n">
-        <v>95135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,64 +1137,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117741560</v>
+        <v>126380336</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NV Bråttjärn, Vrm</t>
+          <t>Villastaden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455666</v>
+        <v>455505</v>
       </c>
       <c r="R6" t="n">
-        <v>6653673</v>
+        <v>6653812</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,12 +1202,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,49 +1216,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Blockig, gammal granskog med inslag av gammal tall.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>På senvuxna, gamla granar. Rikligt spritt.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # På senvuxna, gamla granar. Rikligt spritt.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1322,16 +1237,11 @@
         <v>117741574</v>
       </c>
       <c r="B7" t="n">
-        <v>91776</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1435,44 +1345,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117741309</v>
+        <v>117741303</v>
       </c>
       <c r="B8" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1535,7 +1438,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre granskog, senvuxet ca 160 år.</t>
+          <t>Äldre granskog, på senvuxna granar flera tussar.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1550,12 +1453,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Torrträd av senvuxen, klen gran.</t>
+          <t>Senvuxna granar.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Torrträd av senvuxen, klen gran.</t>
+          <t>Picea abies # Senvuxna granar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1573,14 +1476,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126380337</v>
+        <v>117741560</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1602,19 +1505,30 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Villastaden, Vrm</t>
+          <t>NV Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455520</v>
+        <v>455666</v>
       </c>
       <c r="R9" t="n">
-        <v>6653752</v>
+        <v>6653673</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1638,12 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,9 +1566,20 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blockig, gammal granskog med inslag av gammal tall.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1665,20 +1590,25 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>På senvuxna, gamla granar. Rikligt spritt.</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # På senvuxna, gamla granar. Rikligt spritt.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1688,11 +1618,11 @@
         <v>126380334</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1797,32 +1727,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126380336</v>
+        <v>126380337</v>
       </c>
       <c r="B11" t="n">
-        <v>96487</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1832,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455505</v>
+        <v>455520</v>
       </c>
       <c r="R11" t="n">
-        <v>6653812</v>
+        <v>6653752</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,6 +1808,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126380335</v>
+        <v>117741509</v>
       </c>
       <c r="B12" t="n">
-        <v>96614</v>
+        <v>79413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,37 +1850,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Villastaden, Vrm</t>
+          <t>V Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455512</v>
+        <v>455543</v>
       </c>
       <c r="R12" t="n">
-        <v>6653807</v>
+        <v>6653723</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1959,12 +1907,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,78 +1921,79 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blockig, gammal granskog med inslag av äldre tall.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126380338</v>
+        <v>117741309</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Villastaden, Vrm</t>
+          <t>V Bråttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455533</v>
+        <v>455508</v>
       </c>
       <c r="R13" t="n">
-        <v>6653753</v>
+        <v>6653742</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,12 +2020,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,9 +2034,20 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre granskog, senvuxet ca 160 år.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2098,20 +2058,25 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Torrträd av senvuxen, klen gran.</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Torrträd av senvuxen, klen gran.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 58718-2021 artfynd.xlsx
+++ b/artfynd/A 58718-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380335</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741262</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380338</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741247</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380336</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741574</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741303</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741560</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1724,6 +1769,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380334</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126380337</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741509</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2080,8 +2140,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117741309</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>